--- a/outputs/trim1_mendiburu/cruce_trim1_mendiburu_compras.xlsx
+++ b/outputs/trim1_mendiburu/cruce_trim1_mendiburu_compras.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Trim 1" sheetId="1" r:id="R2a6ae3b47f884674"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle ventas" sheetId="2" r:id="R01caf12b7f81445b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Trim 1" sheetId="1" r:id="Re197e9d39e4d43c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detalle ventas" sheetId="2" r:id="R515a865fdb1644d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -427,10 +427,10 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="E4" s="12" t="n">
-        <x:v>181</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="F4" s="12" t="n">
-        <x:v>260195</x:v>
+        <x:v>263982</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2608,28 +2608,28 @@
         <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J45" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K45" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K45" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L45" t="n">
-        <x:v>3158</x:v>
+        <x:v>4147</x:v>
       </x:c>
       <x:c r="M45" t="n">
-        <x:v>3158</x:v>
+        <x:v>4147</x:v>
       </x:c>
       <x:c r="N45" t="str">
         <x:v>17/06/2026</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>31/08/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P45" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q45" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R45" t="n">
         <x:v>0</x:v>
@@ -3178,28 +3178,28 @@
         <x:v>51941568528</x:v>
       </x:c>
       <x:c r="J55" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K55" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K55" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="L55" t="n">
-        <x:v>2158</x:v>
+        <x:v>2737</x:v>
       </x:c>
       <x:c r="M55" t="n">
-        <x:v>2158</x:v>
+        <x:v>2737</x:v>
       </x:c>
       <x:c r="N55" t="str">
         <x:v>13/07/2026</x:v>
       </x:c>
       <x:c r="O55" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P55" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q55" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R55" t="n">
         <x:v>0</x:v>
@@ -3349,28 +3349,28 @@
         <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J58" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K58" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K58" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="L58" t="n">
-        <x:v>4438</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="M58" t="n">
-        <x:v>4438</x:v>
+        <x:v>6657</x:v>
       </x:c>
       <x:c r="N58" t="str">
         <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="O58" t="str">
-        <x:v>27/08/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P58" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="Q58" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="R58" t="n">
         <x:v>0</x:v>
@@ -4415,11 +4415,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G77" t="str">
-        <x:v>Lucienne Freund Thurne</x:v>
-      </x:c>
-      <x:c r="H77" t="str"/>
+        <x:v>Lucianne Mariana Freundt Thurne</x:v>
+      </x:c>
+      <x:c r="H77" t="str">
+        <x:v>07824185</x:v>
+      </x:c>
       <x:c r="I77" t="str">
-        <x:v>945018132</x:v>
+        <x:v>51945018132</x:v>
       </x:c>
       <x:c r="J77" t="n">
         <x:v>1</x:v>
@@ -4440,7 +4442,7 @@
         <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P77" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="Q77" t="n">
         <x:v>0</x:v>
@@ -11869,10 +11871,10 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B121" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="C121" t="str">
-        <x:v>997921230</x:v>
+        <x:v>955929014</x:v>
       </x:c>
       <x:c r="D121" t="n">
         <x:v>1900</x:v>
@@ -11884,46 +11886,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G121" t="str">
-        <x:v>Beto Mendez</x:v>
+        <x:v>Manuel Montes de Oca</x:v>
       </x:c>
       <x:c r="H121" t="str">
-        <x:v>08275871</x:v>
+        <x:v>42816308</x:v>
       </x:c>
       <x:c r="I121" t="str">
-        <x:v>51997921230</x:v>
+        <x:v>51955929014</x:v>
       </x:c>
       <x:c r="J121" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K121" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L121" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M121" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N121" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="O121" t="str">
-        <x:v>19/06/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P121" t="str">
-        <x:v>04/07/2026</x:v>
+        <x:v>30/10/2026</x:v>
       </x:c>
       <x:c r="Q121" t="n">
-        <x:v>1000</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="R121" t="n">
-        <x:v>1000</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="S121" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T121" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -11955,37 +11957,37 @@
         <x:v>51997921230</x:v>
       </x:c>
       <x:c r="J122" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K122" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L122" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M122" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N122" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="O122" t="str">
-        <x:v>30/06/2026</x:v>
+        <x:v>19/06/2026</x:v>
       </x:c>
       <x:c r="P122" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>04/07/2026</x:v>
       </x:c>
       <x:c r="Q122" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R122" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S122" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T122" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -11993,61 +11995,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B123" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Beto Mendez</x:v>
       </x:c>
       <x:c r="C123" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>997921230</x:v>
       </x:c>
       <x:c r="D123" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E123" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F123" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G123" t="str">
-        <x:v>Nadia Gutierrez</x:v>
+        <x:v>Beto Mendez</x:v>
       </x:c>
       <x:c r="H123" t="str">
-        <x:v>7770642o</x:v>
+        <x:v>08275871</x:v>
       </x:c>
       <x:c r="I123" t="str">
-        <x:v>51987504234</x:v>
+        <x:v>51997921230</x:v>
       </x:c>
       <x:c r="J123" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K123" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L123" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M123" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N123" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="O123" t="str">
-        <x:v>25/06/2026</x:v>
+        <x:v>30/06/2026</x:v>
       </x:c>
       <x:c r="P123" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="Q123" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R123" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S123" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T123" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -12076,40 +12078,40 @@
         <x:v>7770642o</x:v>
       </x:c>
       <x:c r="I124" t="str">
-        <x:v>987504234</x:v>
+        <x:v>51987504234</x:v>
       </x:c>
       <x:c r="J124" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K124" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L124" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M124" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N124" t="str">
-        <x:v>20/07/2026</x:v>
+        <x:v>25/06/2026</x:v>
       </x:c>
       <x:c r="O124" t="str">
-        <x:v>20/07/2026</x:v>
+        <x:v>25/06/2026</x:v>
       </x:c>
       <x:c r="P124" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="Q124" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R124" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S124" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T124" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -12117,61 +12119,61 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B125" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Nadia Gutierrez</x:v>
       </x:c>
       <x:c r="C125" t="str">
-        <x:v>969714361</x:v>
+        <x:v>51987504234</x:v>
       </x:c>
       <x:c r="D125" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E125" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="F125" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G125" t="str">
-        <x:v>Paolo Arauco</x:v>
+        <x:v>Nadia Gutierrez</x:v>
       </x:c>
       <x:c r="H125" t="str">
-        <x:v>71454737</x:v>
+        <x:v>7770642o</x:v>
       </x:c>
       <x:c r="I125" t="str">
-        <x:v>51969714361</x:v>
+        <x:v>987504234</x:v>
       </x:c>
       <x:c r="J125" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K125" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L125" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M125" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N125" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="O125" t="str">
-        <x:v>26/06/2026</x:v>
+        <x:v>20/07/2026</x:v>
       </x:c>
       <x:c r="P125" t="str">
-        <x:v>11/07/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="Q125" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R125" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S125" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T125" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -12200,40 +12202,40 @@
         <x:v>71454737</x:v>
       </x:c>
       <x:c r="I126" t="str">
-        <x:v>969714361</x:v>
+        <x:v>51969714361</x:v>
       </x:c>
       <x:c r="J126" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K126" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L126" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M126" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N126" t="str">
-        <x:v>08/07/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O126" t="str">
-        <x:v>10/07/2026</x:v>
+        <x:v>26/06/2026</x:v>
       </x:c>
       <x:c r="P126" t="str">
-        <x:v>09/08/2026</x:v>
+        <x:v>11/07/2026</x:v>
       </x:c>
       <x:c r="Q126" t="n">
-        <x:v>3029</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R126" t="n">
-        <x:v>3029</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S126" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T126" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -12241,34 +12243,34 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B127" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Paolo Arauco</x:v>
       </x:c>
       <x:c r="C127" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>969714361</x:v>
       </x:c>
       <x:c r="D127" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E127" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F127" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G127" t="str">
-        <x:v>Eduardo Teran</x:v>
+        <x:v>Paolo Arauco</x:v>
       </x:c>
       <x:c r="H127" t="str">
-        <x:v>10439108</x:v>
+        <x:v>71454737</x:v>
       </x:c>
       <x:c r="I127" t="str">
-        <x:v>51949429958</x:v>
+        <x:v>969714361</x:v>
       </x:c>
       <x:c r="J127" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K127" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L127" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -12277,25 +12279,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N127" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>08/07/2026</x:v>
       </x:c>
       <x:c r="O127" t="str">
-        <x:v>24/06/2026</x:v>
+        <x:v>10/07/2026</x:v>
       </x:c>
       <x:c r="P127" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>09/08/2026</x:v>
       </x:c>
       <x:c r="Q127" t="n">
-        <x:v>2219</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R127" t="n">
-        <x:v>2219</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S127" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T127" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -12327,37 +12329,37 @@
         <x:v>51949429958</x:v>
       </x:c>
       <x:c r="J128" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K128" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L128" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M128" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N128" t="str">
-        <x:v>05/08/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="O128" t="str">
-        <x:v>05/08/2026</x:v>
+        <x:v>24/06/2026</x:v>
       </x:c>
       <x:c r="P128" t="str">
-        <x:v>06/08/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="Q128" t="n">
-        <x:v>277</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R128" t="n">
-        <x:v>277</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S128" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T128" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -12365,55 +12367,55 @@
         <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B129" t="str">
-        <x:v>Mayte Carolina Pachas Paulino</x:v>
+        <x:v>Eduardo Teran</x:v>
       </x:c>
       <x:c r="C129" t="str">
-        <x:v>51995551847</x:v>
+        <x:v>51949429958</x:v>
       </x:c>
       <x:c r="D129" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E129" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F129" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G129" t="str">
-        <x:v>MAYTE CAROLINA PACHAS PAULINO</x:v>
+        <x:v>Eduardo Teran</x:v>
       </x:c>
       <x:c r="H129" t="str">
-        <x:v>47665207</x:v>
+        <x:v>10439108</x:v>
       </x:c>
       <x:c r="I129" t="str">
-        <x:v>51995551847</x:v>
+        <x:v>51949429958</x:v>
       </x:c>
       <x:c r="J129" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K129" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L129" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M129" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N129" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="O129" t="str">
-        <x:v>27/06/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="P129" t="str">
-        <x:v>12/07/2026</x:v>
+        <x:v>06/08/2026</x:v>
       </x:c>
       <x:c r="Q129" t="n">
-        <x:v>1000</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="R129" t="n">
-        <x:v>1000</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="S129" t="n">
         <x:v>0</x:v>
@@ -12424,31 +12426,31 @@
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="str">
-        <x:v>Julio 2026</x:v>
+        <x:v>Junio 2026</x:v>
       </x:c>
       <x:c r="B130" t="str">
-        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+        <x:v>Mayte Carolina Pachas Paulino</x:v>
       </x:c>
       <x:c r="C130" t="str">
-        <x:v>999459492</x:v>
+        <x:v>51995551847</x:v>
       </x:c>
       <x:c r="D130" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E130" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Mirko</x:v>
       </x:c>
       <x:c r="F130" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G130" t="str">
-        <x:v>Javier Eduardo Bless Cabrejos</x:v>
+        <x:v>MAYTE CAROLINA PACHAS PAULINO</x:v>
       </x:c>
       <x:c r="H130" t="str">
-        <x:v>10374186</x:v>
+        <x:v>47665207</x:v>
       </x:c>
       <x:c r="I130" t="str">
-        <x:v>999459492</x:v>
+        <x:v>51995551847</x:v>
       </x:c>
       <x:c r="J130" t="str">
         <x:v>Nuevo</x:v>
@@ -12460,28 +12462,28 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M130" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N130" t="str">
-        <x:v>01/07/2026</x:v>
+        <x:v>27/06/2026</x:v>
       </x:c>
       <x:c r="O130" t="str">
-        <x:v>01/07/2026</x:v>
+        <x:v>27/06/2026</x:v>
       </x:c>
       <x:c r="P130" t="str">
-        <x:v>31/07/2026</x:v>
+        <x:v>12/07/2026</x:v>
       </x:c>
       <x:c r="Q130" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R130" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S130" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T130" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -12513,37 +12515,37 @@
         <x:v>999459492</x:v>
       </x:c>
       <x:c r="J131" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K131" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L131" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M131" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N131" t="str">
-        <x:v>21/08/2026</x:v>
+        <x:v>01/07/2026</x:v>
       </x:c>
       <x:c r="O131" t="str">
-        <x:v>21/08/2026</x:v>
+        <x:v>01/07/2026</x:v>
       </x:c>
       <x:c r="P131" t="str">
-        <x:v>14/09/2026</x:v>
+        <x:v>31/07/2026</x:v>
       </x:c>
       <x:c r="Q131" t="n">
-        <x:v>2016</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R131" t="n">
-        <x:v>2016</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S131" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T131" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -12551,61 +12553,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B132" t="str">
-        <x:v>Nathaly Belapatiño</x:v>
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
       </x:c>
       <x:c r="C132" t="str">
-        <x:v>993879277</x:v>
+        <x:v>999459492</x:v>
       </x:c>
       <x:c r="D132" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E132" t="str">
-        <x:v>Web</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F132" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G132" t="str">
-        <x:v>Nathaly Belapatiño</x:v>
+        <x:v>Javier Eduardo Bless Cabrejos</x:v>
       </x:c>
       <x:c r="H132" t="str">
-        <x:v>76397222</x:v>
+        <x:v>10374186</x:v>
       </x:c>
       <x:c r="I132" t="str">
-        <x:v>993879277</x:v>
+        <x:v>999459492</x:v>
       </x:c>
       <x:c r="J132" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K132" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L132" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M132" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N132" t="str">
-        <x:v>02/07/2026</x:v>
+        <x:v>21/08/2026</x:v>
       </x:c>
       <x:c r="O132" t="str">
-        <x:v>02/07/2026</x:v>
+        <x:v>21/08/2026</x:v>
       </x:c>
       <x:c r="P132" t="str">
-        <x:v>17/07/2026</x:v>
+        <x:v>14/09/2026</x:v>
       </x:c>
       <x:c r="Q132" t="n">
-        <x:v>1000</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="R132" t="n">
-        <x:v>1000</x:v>
+        <x:v>2016</x:v>
       </x:c>
       <x:c r="S132" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T132" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -12637,37 +12639,37 @@
         <x:v>993879277</x:v>
       </x:c>
       <x:c r="J133" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K133" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L133" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M133" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N133" t="str">
-        <x:v>15/07/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="O133" t="str">
-        <x:v>15/07/2026</x:v>
+        <x:v>02/07/2026</x:v>
       </x:c>
       <x:c r="P133" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>17/07/2026</x:v>
       </x:c>
       <x:c r="Q133" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R133" t="n">
-        <x:v>779</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S133" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T133" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -12675,55 +12677,55 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B134" t="str">
-        <x:v>Sve Chang</x:v>
+        <x:v>Nathaly Belapatiño</x:v>
       </x:c>
       <x:c r="C134" t="str">
-        <x:v>986185776</x:v>
+        <x:v>993879277</x:v>
       </x:c>
       <x:c r="D134" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E134" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>Web</x:v>
       </x:c>
       <x:c r="F134" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G134" t="str">
-        <x:v>SVE CHANG</x:v>
+        <x:v>Nathaly Belapatiño</x:v>
       </x:c>
       <x:c r="H134" t="str">
-        <x:v>78007264</x:v>
+        <x:v>76397222</x:v>
       </x:c>
       <x:c r="I134" t="str">
-        <x:v>51 986 185 776</x:v>
+        <x:v>993879277</x:v>
       </x:c>
       <x:c r="J134" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K134" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L134" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M134" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N134" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>15/07/2026</x:v>
       </x:c>
       <x:c r="O134" t="str">
-        <x:v>03/07/2026</x:v>
+        <x:v>15/07/2026</x:v>
       </x:c>
       <x:c r="P134" t="str">
-        <x:v>18/07/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="Q134" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="R134" t="n">
-        <x:v>1000</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="S134" t="n">
         <x:v>0</x:v>
@@ -12737,13 +12739,13 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B135" t="str">
-        <x:v>Carolina Hiraoka</x:v>
+        <x:v>Sve Chang</x:v>
       </x:c>
       <x:c r="C135" t="str">
-        <x:v>940219366</x:v>
+        <x:v>986185776</x:v>
       </x:c>
       <x:c r="D135" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E135" t="str">
         <x:v>Linktree</x:v>
@@ -12752,46 +12754,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G135" t="str">
-        <x:v>Carolina Hiraoka</x:v>
+        <x:v>SVE CHANG</x:v>
       </x:c>
       <x:c r="H135" t="str">
-        <x:v>45267059</x:v>
+        <x:v>78007264</x:v>
       </x:c>
       <x:c r="I135" t="str">
-        <x:v>940 219 366</x:v>
+        <x:v>51 986 185 776</x:v>
       </x:c>
       <x:c r="J135" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K135" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L135" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M135" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N135" t="str">
-        <x:v>06/07/2026</x:v>
+        <x:v>03/07/2026</x:v>
       </x:c>
       <x:c r="O135" t="str">
-        <x:v>06/07/2026</x:v>
+        <x:v>03/07/2026</x:v>
       </x:c>
       <x:c r="P135" t="str">
-        <x:v>05/08/2026</x:v>
+        <x:v>18/07/2026</x:v>
       </x:c>
       <x:c r="Q135" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R135" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S135" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T135" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -12823,10 +12825,10 @@
         <x:v>940 219 366</x:v>
       </x:c>
       <x:c r="J136" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K136" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L136" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -12835,13 +12837,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N136" t="str">
-        <x:v>03/08/2026</x:v>
+        <x:v>06/07/2026</x:v>
       </x:c>
       <x:c r="O136" t="str">
-        <x:v>03/08/2026</x:v>
+        <x:v>06/07/2026</x:v>
       </x:c>
       <x:c r="P136" t="str">
-        <x:v>02/09/2026</x:v>
+        <x:v>05/08/2026</x:v>
       </x:c>
       <x:c r="Q136" t="n">
         <x:v>2219</x:v>
@@ -12853,7 +12855,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T136" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -12897,13 +12899,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N137" t="str">
-        <x:v>31/08/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="O137" t="str">
-        <x:v>31/08/2026</x:v>
+        <x:v>03/08/2026</x:v>
       </x:c>
       <x:c r="P137" t="str">
-        <x:v>30/09/2026</x:v>
+        <x:v>02/09/2026</x:v>
       </x:c>
       <x:c r="Q137" t="n">
         <x:v>2219</x:v>
@@ -12959,25 +12961,25 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N138" t="str">
-        <x:v>23/09/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="O138" t="str">
-        <x:v>23/09/2026</x:v>
+        <x:v>31/08/2026</x:v>
       </x:c>
       <x:c r="P138" t="str">
-        <x:v>23/10/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="Q138" t="n">
-        <x:v>3029</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R138" t="n">
-        <x:v>3029</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S138" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T138" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -12985,13 +12987,13 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B139" t="str">
-        <x:v>Diego Mariño</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="C139" t="str">
-        <x:v>941568528</x:v>
+        <x:v>940219366</x:v>
       </x:c>
       <x:c r="D139" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E139" t="str">
         <x:v>Linktree</x:v>
@@ -13000,46 +13002,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G139" t="str">
-        <x:v>Diego Mariño</x:v>
+        <x:v>Carolina Hiraoka</x:v>
       </x:c>
       <x:c r="H139" t="str">
-        <x:v>009248655</x:v>
+        <x:v>45267059</x:v>
       </x:c>
       <x:c r="I139" t="str">
-        <x:v>51941568528</x:v>
+        <x:v>940 219 366</x:v>
       </x:c>
       <x:c r="J139" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K139" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L139" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M139" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N139" t="str">
-        <x:v>13/07/2026</x:v>
+        <x:v>23/09/2026</x:v>
       </x:c>
       <x:c r="O139" t="str">
-        <x:v>13/07/2026</x:v>
+        <x:v>23/09/2026</x:v>
       </x:c>
       <x:c r="P139" t="str">
-        <x:v>28/07/2026</x:v>
+        <x:v>23/10/2026</x:v>
       </x:c>
       <x:c r="Q139" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="R139" t="n">
-        <x:v>1000</x:v>
+        <x:v>3029</x:v>
       </x:c>
       <x:c r="S139" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T139" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -13071,37 +13073,37 @@
         <x:v>51941568528</x:v>
       </x:c>
       <x:c r="J140" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K140" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L140" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M140" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N140" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>13/07/2026</x:v>
       </x:c>
       <x:c r="O140" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>13/07/2026</x:v>
       </x:c>
       <x:c r="P140" t="str">
-        <x:v>22/08/2026</x:v>
+        <x:v>28/07/2026</x:v>
       </x:c>
       <x:c r="Q140" t="n">
-        <x:v>579</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R140" t="n">
-        <x:v>579</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S140" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T140" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -13130,7 +13132,7 @@
         <x:v>009248655</x:v>
       </x:c>
       <x:c r="I141" t="str">
-        <x:v>941568528</x:v>
+        <x:v>51941568528</x:v>
       </x:c>
       <x:c r="J141" t="str">
         <x:v>Renovacion</x:v>
@@ -13145,13 +13147,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N141" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O141" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P141" t="str">
-        <x:v>01/10/2026</x:v>
+        <x:v>22/08/2026</x:v>
       </x:c>
       <x:c r="Q141" t="n">
         <x:v>579</x:v>
@@ -13171,28 +13173,28 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B142" t="str">
-        <x:v>Marcela Noblecilla</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="C142" t="str">
-        <x:v>998678319</x:v>
+        <x:v>941568528</x:v>
       </x:c>
       <x:c r="D142" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E142" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F142" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G142" t="str">
-        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="H142" t="str">
-        <x:v>10058157</x:v>
+        <x:v>009248655</x:v>
       </x:c>
       <x:c r="I142" t="str">
-        <x:v>51998 678 319</x:v>
+        <x:v>941568528</x:v>
       </x:c>
       <x:c r="J142" t="str">
         <x:v>Renovacion</x:v>
@@ -13201,31 +13203,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L142" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M142" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N142" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="O142" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="P142" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>01/10/2026</x:v>
       </x:c>
       <x:c r="Q142" t="n">
-        <x:v>900</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R142" t="n">
-        <x:v>900</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S142" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T142" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -13233,61 +13235,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B143" t="str">
-        <x:v>Marcela Noblecilla</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="C143" t="str">
-        <x:v>998678319</x:v>
+        <x:v>941568528</x:v>
       </x:c>
       <x:c r="D143" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E143" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F143" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G143" t="str">
-        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
+        <x:v>Diego Mariño</x:v>
       </x:c>
       <x:c r="H143" t="str">
-        <x:v>10058157</x:v>
+        <x:v>009248655</x:v>
       </x:c>
       <x:c r="I143" t="str">
-        <x:v>51998 678 319</x:v>
+        <x:v>941568528</x:v>
       </x:c>
       <x:c r="J143" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K143" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L143" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M143" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N143" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="O143" t="str">
-        <x:v>23/07/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P143" t="str">
-        <x:v>07/08/2026</x:v>
+        <x:v>30/10/2026</x:v>
       </x:c>
       <x:c r="Q143" t="n">
-        <x:v>1000</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="R143" t="n">
-        <x:v>1000</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="S143" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T143" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -13325,31 +13327,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L144" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M144" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N144" t="str">
-        <x:v>15/09/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O144" t="str">
-        <x:v>15/09/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P144" t="str">
-        <x:v>15/10/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="Q144" t="n">
-        <x:v>1385</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R144" t="n">
-        <x:v>1385</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S144" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T144" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -13357,61 +13359,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B145" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Marcela Noblecilla</x:v>
       </x:c>
       <x:c r="C145" t="str">
-        <x:v>992978868</x:v>
+        <x:v>998678319</x:v>
       </x:c>
       <x:c r="D145" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E145" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F145" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G145" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
       </x:c>
       <x:c r="H145" t="str">
-        <x:v>09339021</x:v>
+        <x:v>10058157</x:v>
       </x:c>
       <x:c r="I145" t="str">
-        <x:v>51992978868</x:v>
+        <x:v>51998 678 319</x:v>
       </x:c>
       <x:c r="J145" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K145" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L145" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M145" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N145" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="O145" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>23/07/2026</x:v>
       </x:c>
       <x:c r="P145" t="str">
-        <x:v>25/07/2026</x:v>
+        <x:v>07/08/2026</x:v>
       </x:c>
       <x:c r="Q145" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R145" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S145" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T145" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -13419,61 +13421,61 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B146" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Marcela Noblecilla</x:v>
       </x:c>
       <x:c r="C146" t="str">
-        <x:v>992978868</x:v>
+        <x:v>998678319</x:v>
       </x:c>
       <x:c r="D146" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E146" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F146" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G146" t="str">
-        <x:v>Rocio Cespedes</x:v>
+        <x:v>Marcela Susana Noblecilla Olaechea</x:v>
       </x:c>
       <x:c r="H146" t="str">
-        <x:v>09339021</x:v>
+        <x:v>10058157</x:v>
       </x:c>
       <x:c r="I146" t="str">
-        <x:v>51992978868</x:v>
+        <x:v>51998 678 319</x:v>
       </x:c>
       <x:c r="J146" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K146" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L146" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M146" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N146" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>15/09/2026</x:v>
       </x:c>
       <x:c r="O146" t="str">
-        <x:v>24/07/2026</x:v>
+        <x:v>15/09/2026</x:v>
       </x:c>
       <x:c r="P146" t="str">
-        <x:v>08/08/2026</x:v>
+        <x:v>15/10/2026</x:v>
       </x:c>
       <x:c r="Q146" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R146" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S146" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T146" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="147">
@@ -13511,31 +13513,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L147" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M147" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N147" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="O147" t="str">
-        <x:v>30/07/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="P147" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>25/07/2026</x:v>
       </x:c>
       <x:c r="Q147" t="n">
-        <x:v>2219</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R147" t="n">
-        <x:v>2219</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S147" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T147" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>SIN VENDEDOR</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -13567,37 +13569,37 @@
         <x:v>51992978868</x:v>
       </x:c>
       <x:c r="J148" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K148" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L148" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M148" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N148" t="str">
-        <x:v>03/09/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="O148" t="str">
-        <x:v>10/09/2026</x:v>
+        <x:v>24/07/2026</x:v>
       </x:c>
       <x:c r="P148" t="str">
-        <x:v>10/10/2026</x:v>
+        <x:v>08/08/2026</x:v>
       </x:c>
       <x:c r="Q148" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R148" t="n">
-        <x:v>2219</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S148" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T148" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -13605,34 +13607,34 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B149" t="str">
-        <x:v>Jacqueline Idiaquez</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="C149" t="str">
-        <x:v>997512348</x:v>
+        <x:v>992978868</x:v>
       </x:c>
       <x:c r="D149" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E149" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F149" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G149" t="str">
-        <x:v>Jacqueline Idiaquez</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="H149" t="str">
-        <x:v>09673494</x:v>
+        <x:v>09339021</x:v>
       </x:c>
       <x:c r="I149" t="str">
-        <x:v>997 512 348</x:v>
+        <x:v>51992978868</x:v>
       </x:c>
       <x:c r="J149" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K149" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L149" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -13659,7 +13661,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T149" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -13667,34 +13669,34 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B150" t="str">
-        <x:v>Jacqueline Idiaquez</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="C150" t="str">
-        <x:v>997512348</x:v>
+        <x:v>992978868</x:v>
       </x:c>
       <x:c r="D150" t="n">
-        <x:v>2219</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E150" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F150" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G150" t="str">
-        <x:v>Jacqueline Idiaquez</x:v>
+        <x:v>Rocio Cespedes</x:v>
       </x:c>
       <x:c r="H150" t="str">
-        <x:v>09673494</x:v>
+        <x:v>09339021</x:v>
       </x:c>
       <x:c r="I150" t="str">
-        <x:v>997 512 348</x:v>
+        <x:v>51992978868</x:v>
       </x:c>
       <x:c r="J150" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K150" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L150" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -13703,13 +13705,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N150" t="str">
-        <x:v>27/08/2026</x:v>
+        <x:v>03/09/2026</x:v>
       </x:c>
       <x:c r="O150" t="str">
-        <x:v>27/08/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="P150" t="str">
-        <x:v>26/09/2026</x:v>
+        <x:v>10/10/2026</x:v>
       </x:c>
       <x:c r="Q150" t="n">
         <x:v>2219</x:v>
@@ -13721,7 +13723,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T150" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -13729,13 +13731,13 @@
         <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B151" t="str">
-        <x:v>Lylian Leon</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="C151" t="str">
-        <x:v>996500716</x:v>
+        <x:v>997512348</x:v>
       </x:c>
       <x:c r="D151" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E151" t="str">
         <x:v>Form Web</x:v>
@@ -13744,13 +13746,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G151" t="str">
-        <x:v>Lylian León</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="H151" t="str">
-        <x:v>07619479</x:v>
+        <x:v>09673494</x:v>
       </x:c>
       <x:c r="I151" t="str">
-        <x:v>996500716</x:v>
+        <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J151" t="str">
         <x:v>Nuevo</x:v>
@@ -13762,22 +13764,22 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M151" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N151" t="str">
-        <x:v>31/07/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="O151" t="str">
-        <x:v>31/07/2026</x:v>
+        <x:v>30/07/2026</x:v>
       </x:c>
       <x:c r="P151" t="str">
-        <x:v>15/08/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="Q151" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R151" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S151" t="n">
         <x:v>0</x:v>
@@ -13788,91 +13790,93 @@
     </x:row>
     <x:row r="152">
       <x:c r="A152" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B152" t="str">
-        <x:v>Karina Saavedra</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="C152" t="str">
-        <x:v>984609397</x:v>
+        <x:v>997512348</x:v>
       </x:c>
       <x:c r="D152" t="n">
-        <x:v>1900</x:v>
-      </x:c>
-      <x:c r="E152" t="str"/>
+        <x:v>2219</x:v>
+      </x:c>
+      <x:c r="E152" t="str">
+        <x:v>Form Web</x:v>
+      </x:c>
       <x:c r="F152" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G152" t="str">
-        <x:v>Karina Saavedra Zarria</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="H152" t="str">
-        <x:v>07628122</x:v>
+        <x:v>09673494</x:v>
       </x:c>
       <x:c r="I152" t="str">
-        <x:v>51984609397</x:v>
+        <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J152" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K152" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L152" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M152" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N152" t="str">
-        <x:v>10/08/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="O152" t="str">
-        <x:v>10/08/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="P152" t="str">
-        <x:v>25/08/2026</x:v>
+        <x:v>26/09/2026</x:v>
       </x:c>
       <x:c r="Q152" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R152" t="n">
-        <x:v>1000</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S152" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T152" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B153" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="C153" t="str">
-        <x:v>977648321</x:v>
+        <x:v>997512348</x:v>
       </x:c>
       <x:c r="D153" t="n">
-        <x:v>1900</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="E153" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F153" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G153" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Jacqueline Idiaquez</x:v>
       </x:c>
       <x:c r="H153" t="str">
-        <x:v>40154559</x:v>
+        <x:v>09673494</x:v>
       </x:c>
       <x:c r="I153" t="str">
-        <x:v>51977648321</x:v>
+        <x:v>997 512 348</x:v>
       </x:c>
       <x:c r="J153" t="str">
         <x:v>Renovacion</x:v>
@@ -13881,87 +13885,87 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L153" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M153" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N153" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="O153" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>30/09/2026</x:v>
       </x:c>
       <x:c r="P153" t="str">
-        <x:v>28/08/2026</x:v>
+        <x:v>30/10/2026</x:v>
       </x:c>
       <x:c r="Q153" t="n">
-        <x:v>1385</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="R153" t="n">
-        <x:v>1385</x:v>
+        <x:v>2219</x:v>
       </x:c>
       <x:c r="S153" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T153" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" t="str">
-        <x:v>Agosto 2026</x:v>
+        <x:v>Julio 2026</x:v>
       </x:c>
       <x:c r="B154" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Lylian Leon</x:v>
       </x:c>
       <x:c r="C154" t="str">
-        <x:v>977648321</x:v>
+        <x:v>996500716</x:v>
       </x:c>
       <x:c r="D154" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E154" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F154" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G154" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Lylian León</x:v>
       </x:c>
       <x:c r="H154" t="str">
-        <x:v>40154559</x:v>
+        <x:v>07619479</x:v>
       </x:c>
       <x:c r="I154" t="str">
-        <x:v>51977648321</x:v>
+        <x:v>996500716</x:v>
       </x:c>
       <x:c r="J154" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K154" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L154" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M154" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N154" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>31/07/2026</x:v>
       </x:c>
       <x:c r="O154" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>31/07/2026</x:v>
       </x:c>
       <x:c r="P154" t="str">
-        <x:v>13/08/2026</x:v>
+        <x:v>15/08/2026</x:v>
       </x:c>
       <x:c r="Q154" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R154" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S154" t="n">
         <x:v>0</x:v>
@@ -13975,28 +13979,26 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B155" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Karina Saavedra</x:v>
       </x:c>
       <x:c r="C155" t="str">
-        <x:v>977648321</x:v>
+        <x:v>984609397</x:v>
       </x:c>
       <x:c r="D155" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E155" t="str">
-        <x:v>DM</x:v>
-      </x:c>
+      <x:c r="E155" t="str"/>
       <x:c r="F155" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G155" t="str">
-        <x:v>Sandra Palomino</x:v>
+        <x:v>Karina Saavedra Zarria</x:v>
       </x:c>
       <x:c r="H155" t="str">
-        <x:v>40154559</x:v>
+        <x:v>07628122</x:v>
       </x:c>
       <x:c r="I155" t="str">
-        <x:v>51977648321</x:v>
+        <x:v>51984609397</x:v>
       </x:c>
       <x:c r="J155" t="str">
         <x:v>Nuevo</x:v>
@@ -14011,13 +14013,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N155" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>10/08/2026</x:v>
       </x:c>
       <x:c r="O155" t="str">
-        <x:v>12/08/2026</x:v>
+        <x:v>10/08/2026</x:v>
       </x:c>
       <x:c r="P155" t="str">
-        <x:v>27/08/2026</x:v>
+        <x:v>25/08/2026</x:v>
       </x:c>
       <x:c r="Q155" t="n">
         <x:v>1000</x:v>
@@ -14037,28 +14039,28 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B156" t="str">
-        <x:v>Jeanne Goncalvez</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="C156" t="str">
-        <x:v>2022790015</x:v>
+        <x:v>977648321</x:v>
       </x:c>
       <x:c r="D156" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E156" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F156" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G156" t="str">
-        <x:v>JEANNE GONCALVEZ</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="H156" t="str">
-        <x:v>20230943</x:v>
+        <x:v>40154559</x:v>
       </x:c>
       <x:c r="I156" t="str">
-        <x:v>51+1 (202) 279-0015</x:v>
+        <x:v>51977648321</x:v>
       </x:c>
       <x:c r="J156" t="str">
         <x:v>Renovacion</x:v>
@@ -14067,25 +14069,25 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L156" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M156" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N156" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="O156" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="P156" t="str">
-        <x:v>15/08/2026</x:v>
+        <x:v>28/08/2026</x:v>
       </x:c>
       <x:c r="Q156" t="n">
-        <x:v>900</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R156" t="n">
-        <x:v>900</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S156" t="n">
         <x:v>0</x:v>
@@ -14099,61 +14101,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B157" t="str">
-        <x:v>Jeanne Goncalvez</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="C157" t="str">
-        <x:v>2022790015</x:v>
+        <x:v>977648321</x:v>
       </x:c>
       <x:c r="D157" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E157" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F157" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G157" t="str">
-        <x:v>JEANNE GONCALVEZ</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="H157" t="str">
-        <x:v>20230943</x:v>
+        <x:v>40154559</x:v>
       </x:c>
       <x:c r="I157" t="str">
-        <x:v>51+1 (202) 279-0015</x:v>
+        <x:v>51977648321</x:v>
       </x:c>
       <x:c r="J157" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K157" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L157" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M157" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N157" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="O157" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="P157" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>13/08/2026</x:v>
       </x:c>
       <x:c r="Q157" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R157" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S157" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T157" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -14161,61 +14163,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B158" t="str">
-        <x:v>Jeanne Goncalvez</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="C158" t="str">
-        <x:v>2022790015</x:v>
+        <x:v>977648321</x:v>
       </x:c>
       <x:c r="D158" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E158" t="str">
-        <x:v>Mirko</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F158" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G158" t="str">
-        <x:v>JEANNE GONCALVEZ</x:v>
+        <x:v>Sandra Palomino</x:v>
       </x:c>
       <x:c r="H158" t="str">
-        <x:v>20230943</x:v>
+        <x:v>40154559</x:v>
       </x:c>
       <x:c r="I158" t="str">
-        <x:v>51+1 (202) 279-0015</x:v>
+        <x:v>51977648321</x:v>
       </x:c>
       <x:c r="J158" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K158" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L158" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M158" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N158" t="str">
-        <x:v>26/08/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="O158" t="str">
-        <x:v>02/09/2026</x:v>
+        <x:v>12/08/2026</x:v>
       </x:c>
       <x:c r="P158" t="str">
-        <x:v>02/10/2026</x:v>
+        <x:v>27/08/2026</x:v>
       </x:c>
       <x:c r="Q158" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R158" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S158" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T158" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -14250,28 +14252,28 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K159" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L159" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M159" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N159" t="str">
-        <x:v>26/09/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O159" t="str">
-        <x:v>28/09/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="P159" t="str">
-        <x:v>28/10/2026</x:v>
+        <x:v>15/08/2026</x:v>
       </x:c>
       <x:c r="Q159" t="n">
-        <x:v>1385</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R159" t="n">
-        <x:v>1385</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S159" t="n">
         <x:v>0</x:v>
@@ -14285,10 +14287,10 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B160" t="str">
-        <x:v>Eduardo Franca</x:v>
+        <x:v>Jeanne Goncalvez</x:v>
       </x:c>
       <x:c r="C160" t="str">
-        <x:v>2025600320</x:v>
+        <x:v>2022790015</x:v>
       </x:c>
       <x:c r="D160" t="n">
         <x:v>1900</x:v>
@@ -14300,25 +14302,25 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G160" t="str">
-        <x:v>EDUARDO FRANCA</x:v>
+        <x:v>JEANNE GONCALVEZ</x:v>
       </x:c>
       <x:c r="H160" t="str">
-        <x:v>20230623</x:v>
+        <x:v>20230943</x:v>
       </x:c>
       <x:c r="I160" t="str">
-        <x:v>51+1 (202) 560-0320</x:v>
+        <x:v>51+1 (202) 279-0015</x:v>
       </x:c>
       <x:c r="J160" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K160" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L160" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M160" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N160" t="str">
         <x:v>14/08/2026</x:v>
@@ -14327,13 +14329,13 @@
         <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="P160" t="str">
-        <x:v>15/08/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="Q160" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R160" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S160" t="n">
         <x:v>0</x:v>
@@ -14347,10 +14349,10 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B161" t="str">
-        <x:v>Eduardo Franca</x:v>
+        <x:v>Jeanne Goncalvez</x:v>
       </x:c>
       <x:c r="C161" t="str">
-        <x:v>2025600320</x:v>
+        <x:v>2022790015</x:v>
       </x:c>
       <x:c r="D161" t="n">
         <x:v>1900</x:v>
@@ -14362,40 +14364,40 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G161" t="str">
-        <x:v>EDUARDO FRANCA</x:v>
+        <x:v>JEANNE GONCALVEZ</x:v>
       </x:c>
       <x:c r="H161" t="str">
-        <x:v>20230623</x:v>
+        <x:v>20230943</x:v>
       </x:c>
       <x:c r="I161" t="str">
-        <x:v>51+1 (202) 560-0320</x:v>
+        <x:v>51+1 (202) 279-0015</x:v>
       </x:c>
       <x:c r="J161" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K161" t="str">
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L161" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M161" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N161" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>26/08/2026</x:v>
       </x:c>
       <x:c r="O161" t="str">
-        <x:v>14/08/2026</x:v>
+        <x:v>02/09/2026</x:v>
       </x:c>
       <x:c r="P161" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>02/10/2026</x:v>
       </x:c>
       <x:c r="Q161" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R161" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S161" t="n">
         <x:v>0</x:v>
@@ -14409,10 +14411,10 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B162" t="str">
-        <x:v>Eduardo Franca</x:v>
+        <x:v>Jeanne Goncalvez</x:v>
       </x:c>
       <x:c r="C162" t="str">
-        <x:v>2025600320</x:v>
+        <x:v>2022790015</x:v>
       </x:c>
       <x:c r="D162" t="n">
         <x:v>1900</x:v>
@@ -14424,13 +14426,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G162" t="str">
-        <x:v>EDUARDO FRANCA</x:v>
+        <x:v>JEANNE GONCALVEZ</x:v>
       </x:c>
       <x:c r="H162" t="str">
-        <x:v>20230623</x:v>
+        <x:v>20230943</x:v>
       </x:c>
       <x:c r="I162" t="str">
-        <x:v>51+1 (202) 560-0320</x:v>
+        <x:v>51+1 (202) 279-0015</x:v>
       </x:c>
       <x:c r="J162" t="str">
         <x:v>Renovacion</x:v>
@@ -14439,25 +14441,25 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L162" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M162" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N162" t="str">
-        <x:v>26/08/2026</x:v>
+        <x:v>26/09/2026</x:v>
       </x:c>
       <x:c r="O162" t="str">
-        <x:v>02/09/2026</x:v>
+        <x:v>28/09/2026</x:v>
       </x:c>
       <x:c r="P162" t="str">
-        <x:v>02/10/2026</x:v>
+        <x:v>28/10/2026</x:v>
       </x:c>
       <x:c r="Q162" t="n">
-        <x:v>2884</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R162" t="n">
-        <x:v>2884</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S162" t="n">
         <x:v>0</x:v>
@@ -14498,28 +14500,28 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K163" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L163" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M163" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N163" t="str">
-        <x:v>26/09/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O163" t="str">
-        <x:v>07/10/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="P163" t="str">
-        <x:v>06/11/2026</x:v>
+        <x:v>15/08/2026</x:v>
       </x:c>
       <x:c r="Q163" t="n">
-        <x:v>2884</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R163" t="n">
-        <x:v>2884</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S163" t="n">
         <x:v>0</x:v>
@@ -14533,59 +14535,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B164" t="str">
-        <x:v>Jacqueline Banchero Herrera</x:v>
+        <x:v>Eduardo Franca</x:v>
       </x:c>
       <x:c r="C164" t="str">
-        <x:v>989174565</x:v>
+        <x:v>2025600320</x:v>
       </x:c>
       <x:c r="D164" t="n">
-        <x:v>2884</x:v>
-      </x:c>
-      <x:c r="E164" t="str"/>
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E164" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
       <x:c r="F164" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G164" t="str">
-        <x:v>Jacqueline Banchero Herrera</x:v>
+        <x:v>EDUARDO FRANCA</x:v>
       </x:c>
       <x:c r="H164" t="str">
-        <x:v>09752091</x:v>
+        <x:v>20230623</x:v>
       </x:c>
       <x:c r="I164" t="str">
-        <x:v>51989174565</x:v>
+        <x:v>51+1 (202) 560-0320</x:v>
       </x:c>
       <x:c r="J164" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K164" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L164" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M164" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N164" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="O164" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>14/08/2026</x:v>
       </x:c>
       <x:c r="P164" t="str">
-        <x:v>17/09/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="Q164" t="n">
-        <x:v>2884</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R164" t="n">
-        <x:v>2884</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S164" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T164" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="165">
@@ -14593,26 +14597,28 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B165" t="str">
-        <x:v>Jacqueline Banchero Herrera</x:v>
+        <x:v>Eduardo Franca</x:v>
       </x:c>
       <x:c r="C165" t="str">
-        <x:v>989174565</x:v>
+        <x:v>2025600320</x:v>
       </x:c>
       <x:c r="D165" t="n">
-        <x:v>2884</x:v>
-      </x:c>
-      <x:c r="E165" t="str"/>
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E165" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
       <x:c r="F165" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G165" t="str">
-        <x:v>Jacqueline Banchero Herrera</x:v>
+        <x:v>EDUARDO FRANCA</x:v>
       </x:c>
       <x:c r="H165" t="str">
-        <x:v>09752091</x:v>
+        <x:v>20230623</x:v>
       </x:c>
       <x:c r="I165" t="str">
-        <x:v>51989174565</x:v>
+        <x:v>51+1 (202) 560-0320</x:v>
       </x:c>
       <x:c r="J165" t="str">
         <x:v>Renovacion</x:v>
@@ -14627,13 +14633,13 @@
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N165" t="str">
-        <x:v>15/09/2026</x:v>
+        <x:v>26/08/2026</x:v>
       </x:c>
       <x:c r="O165" t="str">
-        <x:v>29/09/2026</x:v>
+        <x:v>02/09/2026</x:v>
       </x:c>
       <x:c r="P165" t="str">
-        <x:v>29/10/2026</x:v>
+        <x:v>02/10/2026</x:v>
       </x:c>
       <x:c r="Q165" t="n">
         <x:v>2884</x:v>
@@ -14653,29 +14659,31 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B166" t="str">
-        <x:v>Maribel Toledo</x:v>
+        <x:v>Eduardo Franca</x:v>
       </x:c>
       <x:c r="C166" t="str">
-        <x:v>949604263</x:v>
+        <x:v>2025600320</x:v>
       </x:c>
       <x:c r="D166" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E166" t="str"/>
+      <x:c r="E166" t="str">
+        <x:v>Mirko</x:v>
+      </x:c>
       <x:c r="F166" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G166" t="str">
-        <x:v>MARIBEL TOLEDO</x:v>
+        <x:v>EDUARDO FRANCA</x:v>
       </x:c>
       <x:c r="H166" t="str">
-        <x:v>10477277</x:v>
+        <x:v>20230623</x:v>
       </x:c>
       <x:c r="I166" t="str">
-        <x:v>51949604263</x:v>
+        <x:v>51+1 (202) 560-0320</x:v>
       </x:c>
       <x:c r="J166" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K166" t="str">
         <x:v>Walk in</x:v>
@@ -14684,28 +14692,28 @@
         <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M166" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N166" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>26/09/2026</x:v>
       </x:c>
       <x:c r="O166" t="str">
-        <x:v>18/08/2026</x:v>
+        <x:v>07/10/2026</x:v>
       </x:c>
       <x:c r="P166" t="str">
-        <x:v>02/09/2026</x:v>
+        <x:v>06/11/2026</x:v>
       </x:c>
       <x:c r="Q166" t="n">
-        <x:v>1000</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="R166" t="n">
-        <x:v>1000</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="S166" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T166" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="167">
@@ -14713,38 +14721,38 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B167" t="str">
-        <x:v>Maribel Toledo</x:v>
+        <x:v>Jacqueline Banchero Herrera</x:v>
       </x:c>
       <x:c r="C167" t="str">
-        <x:v>949604263</x:v>
+        <x:v>989174565</x:v>
       </x:c>
       <x:c r="D167" t="n">
-        <x:v>1900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="E167" t="str"/>
       <x:c r="F167" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G167" t="str">
-        <x:v>MARIBEL TOLEDO</x:v>
+        <x:v>Jacqueline Banchero Herrera</x:v>
       </x:c>
       <x:c r="H167" t="str">
-        <x:v>10477277</x:v>
+        <x:v>09752091</x:v>
       </x:c>
       <x:c r="I167" t="str">
-        <x:v>51949604263</x:v>
+        <x:v>51989174565</x:v>
       </x:c>
       <x:c r="J167" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K167" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L167" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M167" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N167" t="str">
         <x:v>18/08/2026</x:v>
@@ -14753,19 +14761,19 @@
         <x:v>18/08/2026</x:v>
       </x:c>
       <x:c r="P167" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>17/09/2026</x:v>
       </x:c>
       <x:c r="Q167" t="n">
-        <x:v>900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="R167" t="n">
-        <x:v>900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="S167" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T167" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="168">
@@ -14773,26 +14781,26 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B168" t="str">
-        <x:v>Maribel Toledo</x:v>
+        <x:v>Jacqueline Banchero Herrera</x:v>
       </x:c>
       <x:c r="C168" t="str">
-        <x:v>949604263</x:v>
+        <x:v>989174565</x:v>
       </x:c>
       <x:c r="D168" t="n">
-        <x:v>1900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="E168" t="str"/>
       <x:c r="F168" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G168" t="str">
-        <x:v>MARIBEL TOLEDO</x:v>
+        <x:v>Jacqueline Banchero Herrera</x:v>
       </x:c>
       <x:c r="H168" t="str">
-        <x:v>10477277</x:v>
+        <x:v>09752091</x:v>
       </x:c>
       <x:c r="I168" t="str">
-        <x:v>51949604263</x:v>
+        <x:v>51989174565</x:v>
       </x:c>
       <x:c r="J168" t="str">
         <x:v>Renovacion</x:v>
@@ -14801,25 +14809,25 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L168" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M168" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N168" t="str">
-        <x:v>08/09/2026</x:v>
+        <x:v>15/09/2026</x:v>
       </x:c>
       <x:c r="O168" t="str">
-        <x:v>10/09/2026</x:v>
+        <x:v>29/09/2026</x:v>
       </x:c>
       <x:c r="P168" t="str">
-        <x:v>10/10/2026</x:v>
+        <x:v>29/10/2026</x:v>
       </x:c>
       <x:c r="Q168" t="n">
-        <x:v>1385</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="R168" t="n">
-        <x:v>1385</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="S168" t="n">
         <x:v>0</x:v>
@@ -14833,59 +14841,59 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B169" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>Maribel Toledo</x:v>
       </x:c>
       <x:c r="C169" t="str">
-        <x:v>997527485</x:v>
+        <x:v>949604263</x:v>
       </x:c>
       <x:c r="D169" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E169" t="str"/>
       <x:c r="F169" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G169" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>MARIBEL TOLEDO</x:v>
       </x:c>
       <x:c r="H169" t="str">
-        <x:v>997527485</x:v>
+        <x:v>10477277</x:v>
       </x:c>
       <x:c r="I169" t="str">
-        <x:v>10545751</x:v>
+        <x:v>51949604263</x:v>
       </x:c>
       <x:c r="J169" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K169" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L169" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M169" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N169" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>18/08/2026</x:v>
       </x:c>
       <x:c r="O169" t="str">
-        <x:v>19/08/2026</x:v>
+        <x:v>18/08/2026</x:v>
       </x:c>
       <x:c r="P169" t="str">
-        <x:v>20/08/2026</x:v>
+        <x:v>02/09/2026</x:v>
       </x:c>
       <x:c r="Q169" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R169" t="n">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S169" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T169" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="170">
@@ -14893,59 +14901,59 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B170" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>Maribel Toledo</x:v>
       </x:c>
       <x:c r="C170" t="str">
-        <x:v>997527485</x:v>
+        <x:v>949604263</x:v>
       </x:c>
       <x:c r="D170" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E170" t="str"/>
       <x:c r="F170" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G170" t="str">
-        <x:v>Silvina Gorbitz</x:v>
+        <x:v>MARIBEL TOLEDO</x:v>
       </x:c>
       <x:c r="H170" t="str">
-        <x:v>997527485</x:v>
+        <x:v>10477277</x:v>
       </x:c>
       <x:c r="I170" t="str">
-        <x:v>10545751</x:v>
+        <x:v>51949604263</x:v>
       </x:c>
       <x:c r="J170" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K170" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L170" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M170" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N170" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="O170" t="str">
+        <x:v>18/08/2026</x:v>
+      </x:c>
+      <x:c r="P170" t="str">
         <x:v>19/08/2026</x:v>
       </x:c>
-      <x:c r="O170" t="str">
-        <x:v>19/08/2026</x:v>
-      </x:c>
-      <x:c r="P170" t="str">
-        <x:v>03/09/2026</x:v>
-      </x:c>
       <x:c r="Q170" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R170" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S170" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T170" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -14953,55 +14961,53 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B171" t="str">
-        <x:v>Sandra Contreras</x:v>
+        <x:v>Maribel Toledo</x:v>
       </x:c>
       <x:c r="C171" t="str">
-        <x:v>948067720</x:v>
+        <x:v>949604263</x:v>
       </x:c>
       <x:c r="D171" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E171" t="str">
-        <x:v>Form Meta</x:v>
-      </x:c>
+      <x:c r="E171" t="str"/>
       <x:c r="F171" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G171" t="str">
-        <x:v>SANDRA CONTRERAS</x:v>
+        <x:v>MARIBEL TOLEDO</x:v>
       </x:c>
       <x:c r="H171" t="str">
-        <x:v>07465701</x:v>
+        <x:v>10477277</x:v>
       </x:c>
       <x:c r="I171" t="str">
-        <x:v>51948706868</x:v>
+        <x:v>51949604263</x:v>
       </x:c>
       <x:c r="J171" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K171" t="str">
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L171" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M171" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N171" t="str">
-        <x:v>24/08/2026</x:v>
+        <x:v>08/09/2026</x:v>
       </x:c>
       <x:c r="O171" t="str">
-        <x:v>24/08/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="P171" t="str">
-        <x:v>08/09/2026</x:v>
+        <x:v>10/10/2026</x:v>
       </x:c>
       <x:c r="Q171" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R171" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S171" t="n">
         <x:v>0</x:v>
@@ -15015,61 +15021,59 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B172" t="str">
-        <x:v>Sandra Contreras</x:v>
+        <x:v>Silvina Gorbitz</x:v>
       </x:c>
       <x:c r="C172" t="str">
-        <x:v>948067720</x:v>
+        <x:v>997527485</x:v>
       </x:c>
       <x:c r="D172" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E172" t="str">
-        <x:v>Form Meta</x:v>
-      </x:c>
+      <x:c r="E172" t="str"/>
       <x:c r="F172" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G172" t="str">
-        <x:v>SANDRA CONTRERAS</x:v>
+        <x:v>Silvina Gorbitz</x:v>
       </x:c>
       <x:c r="H172" t="str">
-        <x:v>07465701</x:v>
+        <x:v>997527485</x:v>
       </x:c>
       <x:c r="I172" t="str">
-        <x:v>51948706868</x:v>
+        <x:v>10545751</x:v>
       </x:c>
       <x:c r="J172" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K172" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L172" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M172" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N172" t="str">
-        <x:v>17/09/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="O172" t="str">
-        <x:v>22/09/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="P172" t="str">
-        <x:v>22/10/2026</x:v>
+        <x:v>20/08/2026</x:v>
       </x:c>
       <x:c r="Q172" t="n">
-        <x:v>1385</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R172" t="n">
-        <x:v>1385</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S172" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T172" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>SIN VENDEDOR</x:v>
       </x:c>
     </x:row>
     <x:row r="173">
@@ -15077,61 +15081,59 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B173" t="str">
-        <x:v>Sandra Contreras</x:v>
+        <x:v>Silvina Gorbitz</x:v>
       </x:c>
       <x:c r="C173" t="str">
-        <x:v>948067720</x:v>
+        <x:v>997527485</x:v>
       </x:c>
       <x:c r="D173" t="n">
         <x:v>1900</x:v>
       </x:c>
-      <x:c r="E173" t="str">
-        <x:v>Form Meta</x:v>
-      </x:c>
+      <x:c r="E173" t="str"/>
       <x:c r="F173" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G173" t="str">
-        <x:v>SANDRA CONTRERAS</x:v>
+        <x:v>Silvina Gorbitz</x:v>
       </x:c>
       <x:c r="H173" t="str">
-        <x:v>07465701</x:v>
+        <x:v>997527485</x:v>
       </x:c>
       <x:c r="I173" t="str">
-        <x:v>51948706868</x:v>
+        <x:v>10545751</x:v>
       </x:c>
       <x:c r="J173" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K173" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L173" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M173" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N173" t="str">
-        <x:v>17/09/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="O173" t="str">
-        <x:v>21/09/2026</x:v>
+        <x:v>19/08/2026</x:v>
       </x:c>
       <x:c r="P173" t="str">
-        <x:v>07/10/2026</x:v>
+        <x:v>03/09/2026</x:v>
       </x:c>
       <x:c r="Q173" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R173" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S173" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T173" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="174">
@@ -15139,10 +15141,10 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B174" t="str">
-        <x:v>Federico Leon</x:v>
+        <x:v>Sandra Contreras</x:v>
       </x:c>
       <x:c r="C174" t="str">
-        <x:v>948687720</x:v>
+        <x:v>948067720</x:v>
       </x:c>
       <x:c r="D174" t="n">
         <x:v>1900</x:v>
@@ -15154,19 +15156,19 @@
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G174" t="str">
-        <x:v>Federico Leon</x:v>
+        <x:v>SANDRA CONTRERAS</x:v>
       </x:c>
       <x:c r="H174" t="str">
-        <x:v>07869853</x:v>
+        <x:v>07465701</x:v>
       </x:c>
       <x:c r="I174" t="str">
-        <x:v>51994687720</x:v>
+        <x:v>51948706868</x:v>
       </x:c>
       <x:c r="J174" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K174" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L174" t="str">
         <x:v>PERSONALIZADO</x:v>
@@ -15175,13 +15177,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N174" t="str">
-        <x:v>25/08/2026</x:v>
+        <x:v>24/08/2026</x:v>
       </x:c>
       <x:c r="O174" t="str">
-        <x:v>25/08/2026</x:v>
+        <x:v>24/08/2026</x:v>
       </x:c>
       <x:c r="P174" t="str">
-        <x:v>09/09/2026</x:v>
+        <x:v>08/09/2026</x:v>
       </x:c>
       <x:c r="Q174" t="n">
         <x:v>1000</x:v>
@@ -15193,7 +15195,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="T174" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="175">
@@ -15201,10 +15203,10 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B175" t="str">
-        <x:v>Federico Leon</x:v>
+        <x:v>Sandra Contreras</x:v>
       </x:c>
       <x:c r="C175" t="str">
-        <x:v>948687720</x:v>
+        <x:v>948067720</x:v>
       </x:c>
       <x:c r="D175" t="n">
         <x:v>1900</x:v>
@@ -15216,13 +15218,13 @@
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G175" t="str">
-        <x:v>Federico Leon</x:v>
+        <x:v>SANDRA CONTRERAS</x:v>
       </x:c>
       <x:c r="H175" t="str">
-        <x:v>07869853</x:v>
+        <x:v>07465701</x:v>
       </x:c>
       <x:c r="I175" t="str">
-        <x:v>51994687720</x:v>
+        <x:v>51948706868</x:v>
       </x:c>
       <x:c r="J175" t="str">
         <x:v>Renovacion</x:v>
@@ -15231,25 +15233,25 @@
         <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L175" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M175" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N175" t="str">
-        <x:v>04/09/2026</x:v>
+        <x:v>17/09/2026</x:v>
       </x:c>
       <x:c r="O175" t="str">
-        <x:v>16/09/2026</x:v>
+        <x:v>22/09/2026</x:v>
       </x:c>
       <x:c r="P175" t="str">
-        <x:v>16/10/2026</x:v>
+        <x:v>22/10/2026</x:v>
       </x:c>
       <x:c r="Q175" t="n">
-        <x:v>2884</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R175" t="n">
-        <x:v>2884</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S175" t="n">
         <x:v>0</x:v>
@@ -15263,61 +15265,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B176" t="str">
-        <x:v>Daniela Door</x:v>
+        <x:v>Sandra Contreras</x:v>
       </x:c>
       <x:c r="C176" t="str">
-        <x:v>997959393</x:v>
+        <x:v>948067720</x:v>
       </x:c>
       <x:c r="D176" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E176" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F176" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G176" t="str">
-        <x:v>Daniela Door</x:v>
+        <x:v>SANDRA CONTRERAS</x:v>
       </x:c>
       <x:c r="H176" t="str">
-        <x:v>07761819</x:v>
+        <x:v>07465701</x:v>
       </x:c>
       <x:c r="I176" t="str">
-        <x:v>51997595393</x:v>
+        <x:v>51948706868</x:v>
       </x:c>
       <x:c r="J176" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K176" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L176" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M176" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N176" t="str">
-        <x:v>28/08/2026</x:v>
+        <x:v>17/09/2026</x:v>
       </x:c>
       <x:c r="O176" t="str">
-        <x:v>28/08/2026</x:v>
+        <x:v>21/09/2026</x:v>
       </x:c>
       <x:c r="P176" t="str">
-        <x:v>12/09/2026</x:v>
+        <x:v>07/10/2026</x:v>
       </x:c>
       <x:c r="Q176" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R176" t="n">
-        <x:v>1000</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S176" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T176" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="177">
@@ -15325,61 +15327,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B177" t="str">
-        <x:v>Daniela Door</x:v>
+        <x:v>Federico Leon</x:v>
       </x:c>
       <x:c r="C177" t="str">
-        <x:v>997959393</x:v>
+        <x:v>948687720</x:v>
       </x:c>
       <x:c r="D177" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E177" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F177" t="str">
         <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G177" t="str">
-        <x:v>Daniela Door</x:v>
+        <x:v>Federico Leon</x:v>
       </x:c>
       <x:c r="H177" t="str">
-        <x:v>07761819</x:v>
+        <x:v>07869853</x:v>
       </x:c>
       <x:c r="I177" t="str">
-        <x:v>51997595393</x:v>
+        <x:v>51994687720</x:v>
       </x:c>
       <x:c r="J177" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K177" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L177" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M177" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N177" t="str">
-        <x:v>15/09/2026</x:v>
+        <x:v>25/08/2026</x:v>
       </x:c>
       <x:c r="O177" t="str">
-        <x:v>15/09/2026</x:v>
+        <x:v>25/08/2026</x:v>
       </x:c>
       <x:c r="P177" t="str">
-        <x:v>15/10/2026</x:v>
+        <x:v>09/09/2026</x:v>
       </x:c>
       <x:c r="Q177" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R177" t="n">
-        <x:v>1385</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S177" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T177" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="178">
@@ -15387,61 +15389,61 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B178" t="str">
-        <x:v>Mariela Espino</x:v>
+        <x:v>Federico Leon</x:v>
       </x:c>
       <x:c r="C178" t="str">
-        <x:v>968765284</x:v>
+        <x:v>948687720</x:v>
       </x:c>
       <x:c r="D178" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E178" t="str">
-        <x:v>DM</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F178" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G178" t="str">
-        <x:v>Mariela Espino</x:v>
+        <x:v>Federico Leon</x:v>
       </x:c>
       <x:c r="H178" t="str">
-        <x:v>21533929</x:v>
+        <x:v>07869853</x:v>
       </x:c>
       <x:c r="I178" t="str">
-        <x:v>51968 765 284</x:v>
+        <x:v>51994687720</x:v>
       </x:c>
       <x:c r="J178" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K178" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L178" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M178" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N178" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>04/09/2026</x:v>
       </x:c>
       <x:c r="O178" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>16/09/2026</x:v>
       </x:c>
       <x:c r="P178" t="str">
-        <x:v>30/08/2026</x:v>
+        <x:v>16/10/2026</x:v>
       </x:c>
       <x:c r="Q178" t="n">
-        <x:v>900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="R178" t="n">
-        <x:v>900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="S178" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T178" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="179">
@@ -15449,10 +15451,10 @@
         <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B179" t="str">
-        <x:v>Mariela Espino</x:v>
+        <x:v>Daniela Door</x:v>
       </x:c>
       <x:c r="C179" t="str">
-        <x:v>968765284</x:v>
+        <x:v>997959393</x:v>
       </x:c>
       <x:c r="D179" t="n">
         <x:v>1900</x:v>
@@ -15461,16 +15463,16 @@
         <x:v>DM</x:v>
       </x:c>
       <x:c r="F179" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G179" t="str">
-        <x:v>Mariela Espino</x:v>
+        <x:v>Daniela Door</x:v>
       </x:c>
       <x:c r="H179" t="str">
-        <x:v>21533929</x:v>
+        <x:v>07761819</x:v>
       </x:c>
       <x:c r="I179" t="str">
-        <x:v>51968 765 284</x:v>
+        <x:v>51997595393</x:v>
       </x:c>
       <x:c r="J179" t="str">
         <x:v>Nuevo</x:v>
@@ -15485,13 +15487,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N179" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>28/08/2026</x:v>
       </x:c>
       <x:c r="O179" t="str">
-        <x:v>29/08/2026</x:v>
+        <x:v>28/08/2026</x:v>
       </x:c>
       <x:c r="P179" t="str">
-        <x:v>13/09/2026</x:v>
+        <x:v>12/09/2026</x:v>
       </x:c>
       <x:c r="Q179" t="n">
         <x:v>1000</x:v>
@@ -15508,31 +15510,31 @@
     </x:row>
     <x:row r="180">
       <x:c r="A180" t="str">
-        <x:v>Septiembre 2026</x:v>
+        <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B180" t="str">
-        <x:v>Ayleen Cisneros</x:v>
+        <x:v>Daniela Door</x:v>
       </x:c>
       <x:c r="C180" t="str">
-        <x:v>999940298</x:v>
+        <x:v>997959393</x:v>
       </x:c>
       <x:c r="D180" t="n">
-        <x:v>7876</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E180" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F180" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G180" t="str">
-        <x:v>Ayleen Cisneros</x:v>
+        <x:v>Daniela Door</x:v>
       </x:c>
       <x:c r="H180" t="str">
-        <x:v>40602386</x:v>
+        <x:v>07761819</x:v>
       </x:c>
       <x:c r="I180" t="str">
-        <x:v>51999940298</x:v>
+        <x:v>51997595393</x:v>
       </x:c>
       <x:c r="J180" t="str">
         <x:v>Renovacion</x:v>
@@ -15541,122 +15543,122 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L180" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M180" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N180" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>15/09/2026</x:v>
       </x:c>
       <x:c r="O180" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>15/09/2026</x:v>
       </x:c>
       <x:c r="P180" t="str">
-        <x:v>01/10/2026</x:v>
+        <x:v>15/10/2026</x:v>
       </x:c>
       <x:c r="Q180" t="n">
-        <x:v>3938</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R180" t="n">
-        <x:v>3938</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S180" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T180" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="181">
       <x:c r="A181" t="str">
-        <x:v>Septiembre 2026</x:v>
+        <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B181" t="str">
-        <x:v>Ayleen Cisneros</x:v>
+        <x:v>Mariela Espino</x:v>
       </x:c>
       <x:c r="C181" t="str">
-        <x:v>999940298</x:v>
+        <x:v>968765284</x:v>
       </x:c>
       <x:c r="D181" t="n">
-        <x:v>7876</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E181" t="str">
-        <x:v>Linktree</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F181" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G181" t="str">
-        <x:v>Ayleen Cisneros</x:v>
+        <x:v>Mariela Espino</x:v>
       </x:c>
       <x:c r="H181" t="str">
-        <x:v>40602386</x:v>
+        <x:v>21533929</x:v>
       </x:c>
       <x:c r="I181" t="str">
-        <x:v>51999940298</x:v>
+        <x:v>51968 765 284</x:v>
       </x:c>
       <x:c r="J181" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K181" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L181" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M181" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N181" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="O181" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="P181" t="str">
-        <x:v>01/10/2026</x:v>
+        <x:v>30/08/2026</x:v>
       </x:c>
       <x:c r="Q181" t="n">
-        <x:v>3938</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R181" t="n">
-        <x:v>3938</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S181" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T181" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>SIN VENDEDOR</x:v>
       </x:c>
     </x:row>
     <x:row r="182">
       <x:c r="A182" t="str">
-        <x:v>Septiembre 2026</x:v>
+        <x:v>Agosto 2026</x:v>
       </x:c>
       <x:c r="B182" t="str">
-        <x:v>Maria Isabel Manzanares</x:v>
+        <x:v>Mariela Espino</x:v>
       </x:c>
       <x:c r="C182" t="str">
-        <x:v>992751660</x:v>
+        <x:v>968765284</x:v>
       </x:c>
       <x:c r="D182" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E182" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>DM</x:v>
       </x:c>
       <x:c r="F182" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G182" t="str">
-        <x:v>Maria Isabel Manzanares</x:v>
+        <x:v>Mariela Espino</x:v>
       </x:c>
       <x:c r="H182" t="str">
-        <x:v>09881455</x:v>
+        <x:v>21533929</x:v>
       </x:c>
       <x:c r="I182" t="str">
-        <x:v>51992751660</x:v>
+        <x:v>51968 765 284</x:v>
       </x:c>
       <x:c r="J182" t="str">
         <x:v>Nuevo</x:v>
@@ -15671,13 +15673,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N182" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="O182" t="str">
-        <x:v>01/09/2026</x:v>
+        <x:v>29/08/2026</x:v>
       </x:c>
       <x:c r="P182" t="str">
-        <x:v>16/09/2026</x:v>
+        <x:v>13/09/2026</x:v>
       </x:c>
       <x:c r="Q182" t="n">
         <x:v>1000</x:v>
@@ -15697,28 +15699,28 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B183" t="str">
-        <x:v>Maria Isabel Manzanares</x:v>
+        <x:v>Ayleen Cisneros</x:v>
       </x:c>
       <x:c r="C183" t="str">
-        <x:v>992751660</x:v>
+        <x:v>999940298</x:v>
       </x:c>
       <x:c r="D183" t="n">
-        <x:v>1900</x:v>
+        <x:v>7876</x:v>
       </x:c>
       <x:c r="E183" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F183" t="str">
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G183" t="str">
-        <x:v>Maria Isabel Manzanares</x:v>
+        <x:v>Ayleen Cisneros</x:v>
       </x:c>
       <x:c r="H183" t="str">
-        <x:v>09881455</x:v>
+        <x:v>40602386</x:v>
       </x:c>
       <x:c r="I183" t="str">
-        <x:v>51992751660</x:v>
+        <x:v>51999940298</x:v>
       </x:c>
       <x:c r="J183" t="str">
         <x:v>Renovacion</x:v>
@@ -15727,31 +15729,31 @@
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L183" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M183" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N183" t="str">
-        <x:v>10/09/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="O183" t="str">
-        <x:v>10/09/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="P183" t="str">
-        <x:v>10/10/2026</x:v>
+        <x:v>01/10/2026</x:v>
       </x:c>
       <x:c r="Q183" t="n">
-        <x:v>1385</x:v>
+        <x:v>3938</x:v>
       </x:c>
       <x:c r="R183" t="n">
-        <x:v>1385</x:v>
+        <x:v>3938</x:v>
       </x:c>
       <x:c r="S183" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T183" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="184">
@@ -15759,61 +15761,61 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B184" t="str">
-        <x:v>Mayde Fernandez</x:v>
+        <x:v>Ayleen Cisneros</x:v>
       </x:c>
       <x:c r="C184" t="str">
-        <x:v>21811801379</x:v>
+        <x:v>999940298</x:v>
       </x:c>
       <x:c r="D184" t="n">
-        <x:v>1900</x:v>
+        <x:v>7876</x:v>
       </x:c>
       <x:c r="E184" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Linktree</x:v>
       </x:c>
       <x:c r="F184" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G184" t="str">
-        <x:v>Mayde Fernandez</x:v>
+        <x:v>Ayleen Cisneros</x:v>
       </x:c>
       <x:c r="H184" t="str">
-        <x:v>005772121</x:v>
+        <x:v>40602386</x:v>
       </x:c>
       <x:c r="I184" t="str">
-        <x:v>515218118013796</x:v>
+        <x:v>51999940298</x:v>
       </x:c>
       <x:c r="J184" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K184" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L184" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M184" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N184" t="str">
-        <x:v>09/09/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="O184" t="str">
-        <x:v>09/09/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="P184" t="str">
-        <x:v>10/09/2026</x:v>
+        <x:v>01/10/2026</x:v>
       </x:c>
       <x:c r="Q184" t="n">
-        <x:v>900</x:v>
+        <x:v>3938</x:v>
       </x:c>
       <x:c r="R184" t="n">
-        <x:v>900</x:v>
+        <x:v>3938</x:v>
       </x:c>
       <x:c r="S184" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T184" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="185">
@@ -15821,28 +15823,28 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B185" t="str">
-        <x:v>Mayde Fernandez</x:v>
+        <x:v>Maria Isabel Manzanares</x:v>
       </x:c>
       <x:c r="C185" t="str">
-        <x:v>21811801379</x:v>
+        <x:v>992751660</x:v>
       </x:c>
       <x:c r="D185" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E185" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F185" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G185" t="str">
-        <x:v>Mayde Fernandez</x:v>
+        <x:v>Maria Isabel Manzanares</x:v>
       </x:c>
       <x:c r="H185" t="str">
-        <x:v>005772121</x:v>
+        <x:v>09881455</x:v>
       </x:c>
       <x:c r="I185" t="str">
-        <x:v>515218118013796</x:v>
+        <x:v>51992751660</x:v>
       </x:c>
       <x:c r="J185" t="str">
         <x:v>Nuevo</x:v>
@@ -15857,13 +15859,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N185" t="str">
-        <x:v>09/09/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="O185" t="str">
-        <x:v>09/09/2026</x:v>
+        <x:v>01/09/2026</x:v>
       </x:c>
       <x:c r="P185" t="str">
-        <x:v>24/09/2026</x:v>
+        <x:v>16/09/2026</x:v>
       </x:c>
       <x:c r="Q185" t="n">
         <x:v>1000</x:v>
@@ -15883,61 +15885,61 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B186" t="str">
-        <x:v>Mayde Fernandez</x:v>
+        <x:v>Maria Isabel Manzanares</x:v>
       </x:c>
       <x:c r="C186" t="str">
-        <x:v>21811801379</x:v>
+        <x:v>992751660</x:v>
       </x:c>
       <x:c r="D186" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E186" t="str">
-        <x:v>Form Web</x:v>
+        <x:v>Form Meta</x:v>
       </x:c>
       <x:c r="F186" t="str">
-        <x:v>Nombre exacto</x:v>
+        <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G186" t="str">
-        <x:v>Mayde Fernandez</x:v>
+        <x:v>Maria Isabel Manzanares</x:v>
       </x:c>
       <x:c r="H186" t="str">
-        <x:v>005772121</x:v>
+        <x:v>09881455</x:v>
       </x:c>
       <x:c r="I186" t="str">
-        <x:v>515218118013796</x:v>
+        <x:v>51992751660</x:v>
       </x:c>
       <x:c r="J186" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K186" t="str">
-        <x:v>Walk in</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L186" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M186" t="str">
         <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N186" t="str">
-        <x:v>21/09/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="O186" t="str">
-        <x:v>23/09/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="P186" t="str">
-        <x:v>01/10/2026</x:v>
+        <x:v>10/10/2026</x:v>
       </x:c>
       <x:c r="Q186" t="n">
-        <x:v>2884</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="R186" t="n">
-        <x:v>2884</x:v>
+        <x:v>1385</x:v>
       </x:c>
       <x:c r="S186" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T186" t="str">
-        <x:v>mafervta</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="187">
@@ -15945,61 +15947,61 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B187" t="str">
-        <x:v>Claudia Vallejos</x:v>
+        <x:v>Mayde Fernandez</x:v>
       </x:c>
       <x:c r="C187" t="str">
-        <x:v>999001683</x:v>
+        <x:v>21811801379</x:v>
       </x:c>
       <x:c r="D187" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E187" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F187" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G187" t="str">
-        <x:v>Claudia Paola Vallejos Araujo</x:v>
+        <x:v>Mayde Fernandez</x:v>
       </x:c>
       <x:c r="H187" t="str">
-        <x:v>09340213</x:v>
+        <x:v>005772121</x:v>
       </x:c>
       <x:c r="I187" t="str">
-        <x:v>999001683</x:v>
+        <x:v>515218118013796</x:v>
       </x:c>
       <x:c r="J187" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K187" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L187" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MATRICULAS</x:v>
       </x:c>
       <x:c r="M187" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 dia</x:v>
       </x:c>
       <x:c r="N187" t="str">
+        <x:v>09/09/2026</x:v>
+      </x:c>
+      <x:c r="O187" t="str">
+        <x:v>09/09/2026</x:v>
+      </x:c>
+      <x:c r="P187" t="str">
         <x:v>10/09/2026</x:v>
       </x:c>
-      <x:c r="O187" t="str">
-        <x:v>10/09/2026</x:v>
-      </x:c>
-      <x:c r="P187" t="str">
-        <x:v>25/09/2026</x:v>
-      </x:c>
       <x:c r="Q187" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="R187" t="n">
-        <x:v>1000</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="S187" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T187" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>SIN VENDEDOR</x:v>
       </x:c>
     </x:row>
     <x:row r="188">
@@ -16007,61 +16009,61 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B188" t="str">
-        <x:v>Claudia Vallejos</x:v>
+        <x:v>Mayde Fernandez</x:v>
       </x:c>
       <x:c r="C188" t="str">
-        <x:v>999001683</x:v>
+        <x:v>21811801379</x:v>
       </x:c>
       <x:c r="D188" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E188" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F188" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G188" t="str">
-        <x:v>Claudia Paola Vallejos Araujo</x:v>
+        <x:v>Mayde Fernandez</x:v>
       </x:c>
       <x:c r="H188" t="str">
-        <x:v>09340213</x:v>
+        <x:v>005772121</x:v>
       </x:c>
       <x:c r="I188" t="str">
-        <x:v>999001683</x:v>
+        <x:v>515218118013796</x:v>
       </x:c>
       <x:c r="J188" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Nuevo</x:v>
       </x:c>
       <x:c r="K188" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Digital</x:v>
       </x:c>
       <x:c r="L188" t="str">
-        <x:v>MEMBRESÍA</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M188" t="str">
-        <x:v>1 mes</x:v>
+        <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N188" t="str">
-        <x:v>25/09/2026</x:v>
+        <x:v>09/09/2026</x:v>
       </x:c>
       <x:c r="O188" t="str">
-        <x:v>25/09/2026</x:v>
+        <x:v>09/09/2026</x:v>
       </x:c>
       <x:c r="P188" t="str">
-        <x:v>25/10/2026</x:v>
+        <x:v>24/09/2026</x:v>
       </x:c>
       <x:c r="Q188" t="n">
-        <x:v>811</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="R188" t="n">
-        <x:v>811</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="S188" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T188" t="str">
-        <x:v>rossiventas</x:v>
+        <x:v>kcossiov</x:v>
       </x:c>
     </x:row>
     <x:row r="189">
@@ -16069,61 +16071,61 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B189" t="str">
-        <x:v>Rosa Manrique</x:v>
+        <x:v>Mayde Fernandez</x:v>
       </x:c>
       <x:c r="C189" t="str">
-        <x:v>997516550</x:v>
+        <x:v>21811801379</x:v>
       </x:c>
       <x:c r="D189" t="n">
         <x:v>1900</x:v>
       </x:c>
       <x:c r="E189" t="str">
-        <x:v>Form Meta</x:v>
+        <x:v>Form Web</x:v>
       </x:c>
       <x:c r="F189" t="str">
-        <x:v>Telefono</x:v>
+        <x:v>Nombre exacto</x:v>
       </x:c>
       <x:c r="G189" t="str">
-        <x:v>Rosa Manrique</x:v>
+        <x:v>Mayde Fernandez</x:v>
       </x:c>
       <x:c r="H189" t="str">
-        <x:v>29592817</x:v>
+        <x:v>005772121</x:v>
       </x:c>
       <x:c r="I189" t="str">
-        <x:v>51997516550</x:v>
+        <x:v>515218118013796</x:v>
       </x:c>
       <x:c r="J189" t="str">
         <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K189" t="str">
-        <x:v>Renovacion</x:v>
+        <x:v>Walk in</x:v>
       </x:c>
       <x:c r="L189" t="str">
-        <x:v>MATRICULAS</x:v>
+        <x:v>PERSONALIZADO</x:v>
       </x:c>
       <x:c r="M189" t="str">
-        <x:v>1 dia</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N189" t="str">
-        <x:v>12/09/2026</x:v>
+        <x:v>21/09/2026</x:v>
       </x:c>
       <x:c r="O189" t="str">
-        <x:v>12/09/2026</x:v>
+        <x:v>23/09/2026</x:v>
       </x:c>
       <x:c r="P189" t="str">
-        <x:v>13/09/2026</x:v>
+        <x:v>01/10/2026</x:v>
       </x:c>
       <x:c r="Q189" t="n">
-        <x:v>900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="R189" t="n">
-        <x:v>900</x:v>
+        <x:v>2884</x:v>
       </x:c>
       <x:c r="S189" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T189" t="str">
-        <x:v>SIN VENDEDOR</x:v>
+        <x:v>mafervta</x:v>
       </x:c>
     </x:row>
     <x:row r="190">
@@ -16131,10 +16133,10 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B190" t="str">
-        <x:v>Rosa Manrique</x:v>
+        <x:v>Claudia Vallejos</x:v>
       </x:c>
       <x:c r="C190" t="str">
-        <x:v>997516550</x:v>
+        <x:v>999001683</x:v>
       </x:c>
       <x:c r="D190" t="n">
         <x:v>1900</x:v>
@@ -16146,13 +16148,13 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G190" t="str">
-        <x:v>Rosa Manrique</x:v>
+        <x:v>Claudia Paola Vallejos Araujo</x:v>
       </x:c>
       <x:c r="H190" t="str">
-        <x:v>29592817</x:v>
+        <x:v>09340213</x:v>
       </x:c>
       <x:c r="I190" t="str">
-        <x:v>51997516550</x:v>
+        <x:v>999001683</x:v>
       </x:c>
       <x:c r="J190" t="str">
         <x:v>Nuevo</x:v>
@@ -16167,13 +16169,13 @@
         <x:v>15 dias</x:v>
       </x:c>
       <x:c r="N190" t="str">
-        <x:v>12/09/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="O190" t="str">
-        <x:v>12/09/2026</x:v>
+        <x:v>10/09/2026</x:v>
       </x:c>
       <x:c r="P190" t="str">
-        <x:v>27/09/2026</x:v>
+        <x:v>25/09/2026</x:v>
       </x:c>
       <x:c r="Q190" t="n">
         <x:v>1000</x:v>
@@ -16193,10 +16195,10 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B191" t="str">
-        <x:v>Jimena Morales</x:v>
+        <x:v>Claudia Vallejos</x:v>
       </x:c>
       <x:c r="C191" t="str">
-        <x:v>994655810</x:v>
+        <x:v>999001683</x:v>
       </x:c>
       <x:c r="D191" t="n">
         <x:v>1900</x:v>
@@ -16208,46 +16210,46 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G191" t="str">
-        <x:v>Jimena Morales</x:v>
+        <x:v>Claudia Paola Vallejos Araujo</x:v>
       </x:c>
       <x:c r="H191" t="str">
-        <x:v>10550906</x:v>
+        <x:v>09340213</x:v>
       </x:c>
       <x:c r="I191" t="str">
-        <x:v>51994655810</x:v>
+        <x:v>999001683</x:v>
       </x:c>
       <x:c r="J191" t="str">
-        <x:v>Nuevo</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="K191" t="str">
-        <x:v>Digital</x:v>
+        <x:v>Renovacion</x:v>
       </x:c>
       <x:c r="L191" t="str">
-        <x:v>PERSONALIZADO</x:v>
+        <x:v>MEMBRESÍA</x:v>
       </x:c>
       <x:c r="M191" t="str">
-        <x:v>15 dias</x:v>
+        <x:v>1 mes</x:v>
       </x:c>
       <x:c r="N191" t="str">
-        <x:v>14/09/2026</x:v>
+        <x:v>25/09/2026</x:v>
       </x:c>
       <x:c r="O191" t="str">
-        <x:v>14/09/2026</x:v>
+        <x:v>25/09/2026</x:v>
       </x:c>
       <x:c r="P191" t="str">
-        <x:v>29/09/2026</x:v>
+        <x:v>25/10/2026</x:v>
       </x:c>
       <x:c r="Q191" t="n">
-        <x:v>1000</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="R191" t="n">
-        <x:v>1000</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="S191" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="T191" t="str">
-        <x:v>kcossiov</x:v>
+        <x:v>rossiventas</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -16255,13 +16257,13 @@
         <x:v>Septiembre 2026</x:v>
       </x:c>
       <x:c r="B192" t="str">
-        <x:v>Lucienne Freund Thurne</x:v>
+        <x:v>Rosa Manrique</x:v>
       </x:c>
       <x:c r="C192" t="str">
-        <x:v>945018132</x:v>
+        <x:v>997516550</x:v>
       </x:c>
       <x:c r="D192" t="n">
-        <x:v>2200</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="E192" t="str">
         <x:v>Form Meta</x:v>
@@ -16270,43 +16272,295 @@
         <x:v>Telefono</x:v>
       </x:c>
       <x:c r="G192" t="str">
+        <x:v>Rosa Manrique</x:v>
+      </x:c>
+      <x:c r="H192" t="str">
+        <x:v>29592817</x:v>
+      </x:c>
+      <x:c r="I192" t="str">
+        <x:v>51997516550</x:v>
+      </x:c>
+      <x:c r="J192" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K192" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L192" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M192" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N192" t="str">
+        <x:v>12/09/2026</x:v>
+      </x:c>
+      <x:c r="O192" t="str">
+        <x:v>12/09/2026</x:v>
+      </x:c>
+      <x:c r="P192" t="str">
+        <x:v>13/09/2026</x:v>
+      </x:c>
+      <x:c r="Q192" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="R192" t="n">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="S192" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T192" t="str">
+        <x:v>SIN VENDEDOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193" t="str">
+        <x:v>Septiembre 2026</x:v>
+      </x:c>
+      <x:c r="B193" t="str">
+        <x:v>Rosa Manrique</x:v>
+      </x:c>
+      <x:c r="C193" t="str">
+        <x:v>997516550</x:v>
+      </x:c>
+      <x:c r="D193" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E193" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F193" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G193" t="str">
+        <x:v>Rosa Manrique</x:v>
+      </x:c>
+      <x:c r="H193" t="str">
+        <x:v>29592817</x:v>
+      </x:c>
+      <x:c r="I193" t="str">
+        <x:v>51997516550</x:v>
+      </x:c>
+      <x:c r="J193" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K193" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L193" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M193" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N193" t="str">
+        <x:v>12/09/2026</x:v>
+      </x:c>
+      <x:c r="O193" t="str">
+        <x:v>12/09/2026</x:v>
+      </x:c>
+      <x:c r="P193" t="str">
+        <x:v>27/09/2026</x:v>
+      </x:c>
+      <x:c r="Q193" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R193" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S193" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T193" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>Septiembre 2026</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>Jimena Morales</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>994655810</x:v>
+      </x:c>
+      <x:c r="D194" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="E194" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F194" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G194" t="str">
+        <x:v>Jimena Morales</x:v>
+      </x:c>
+      <x:c r="H194" t="str">
+        <x:v>10550906</x:v>
+      </x:c>
+      <x:c r="I194" t="str">
+        <x:v>51994655810</x:v>
+      </x:c>
+      <x:c r="J194" t="str">
+        <x:v>Nuevo</x:v>
+      </x:c>
+      <x:c r="K194" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L194" t="str">
+        <x:v>PERSONALIZADO</x:v>
+      </x:c>
+      <x:c r="M194" t="str">
+        <x:v>15 dias</x:v>
+      </x:c>
+      <x:c r="N194" t="str">
+        <x:v>14/09/2026</x:v>
+      </x:c>
+      <x:c r="O194" t="str">
+        <x:v>14/09/2026</x:v>
+      </x:c>
+      <x:c r="P194" t="str">
+        <x:v>29/09/2026</x:v>
+      </x:c>
+      <x:c r="Q194" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R194" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S194" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T194" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>Septiembre 2026</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
         <x:v>Lucienne Freund Thurne</x:v>
       </x:c>
-      <x:c r="H192" t="str"/>
-      <x:c r="I192" t="str">
+      <x:c r="C195" t="str">
         <x:v>945018132</x:v>
       </x:c>
-      <x:c r="J192" t="str">
+      <x:c r="D195" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G195" t="str">
+        <x:v>Lucianne Mariana Freundt Thurne</x:v>
+      </x:c>
+      <x:c r="H195" t="str">
+        <x:v>07824185</x:v>
+      </x:c>
+      <x:c r="I195" t="str">
+        <x:v>51945018132</x:v>
+      </x:c>
+      <x:c r="J195" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="K195" t="str">
+        <x:v>Renovacion</x:v>
+      </x:c>
+      <x:c r="L195" t="str">
+        <x:v>MATRICULAS</x:v>
+      </x:c>
+      <x:c r="M195" t="str">
+        <x:v>1 dia</x:v>
+      </x:c>
+      <x:c r="N195" t="str">
+        <x:v>30/09/2026</x:v>
+      </x:c>
+      <x:c r="O195" t="str">
+        <x:v>30/09/2026</x:v>
+      </x:c>
+      <x:c r="P195" t="str">
+        <x:v>01/10/2026</x:v>
+      </x:c>
+      <x:c r="Q195" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="R195" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="S195" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T195" t="str">
+        <x:v>SIN VENDEDOR</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196" t="str">
+        <x:v>Septiembre 2026</x:v>
+      </x:c>
+      <x:c r="B196" t="str">
+        <x:v>Lucienne Freund Thurne</x:v>
+      </x:c>
+      <x:c r="C196" t="str">
+        <x:v>945018132</x:v>
+      </x:c>
+      <x:c r="D196" t="n">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="E196" t="str">
+        <x:v>Form Meta</x:v>
+      </x:c>
+      <x:c r="F196" t="str">
+        <x:v>Telefono</x:v>
+      </x:c>
+      <x:c r="G196" t="str">
+        <x:v>Lucianne Mariana Freundt Thurne</x:v>
+      </x:c>
+      <x:c r="H196" t="str">
+        <x:v>07824185</x:v>
+      </x:c>
+      <x:c r="I196" t="str">
+        <x:v>51945018132</x:v>
+      </x:c>
+      <x:c r="J196" t="str">
         <x:v>Nuevo</x:v>
       </x:c>
-      <x:c r="K192" t="str">
-        <x:v>Form Meta</x:v>
-      </x:c>
-      <x:c r="L192" t="str">
+      <x:c r="K196" t="str">
+        <x:v>Digital</x:v>
+      </x:c>
+      <x:c r="L196" t="str">
         <x:v>PERSONALIZADO</x:v>
       </x:c>
-      <x:c r="M192" t="str">
+      <x:c r="M196" t="str">
         <x:v>15 dias</x:v>
       </x:c>
-      <x:c r="N192" t="str">
+      <x:c r="N196" t="str">
         <x:v>30/09/2026</x:v>
       </x:c>
-      <x:c r="O192" t="str">
+      <x:c r="O196" t="str">
         <x:v>30/09/2026</x:v>
       </x:c>
-      <x:c r="P192" t="str">
+      <x:c r="P196" t="str">
         <x:v>15/10/2026</x:v>
       </x:c>
-      <x:c r="Q192" t="n">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="R192" t="n">
-        <x:v>2200</x:v>
-      </x:c>
-      <x:c r="S192" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="T192" t="str"/>
+      <x:c r="Q196" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="R196" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="S196" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T196" t="str">
+        <x:v>kcossiov</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
